--- a/Output/raw_attributes_dictionary.xlsx
+++ b/Output/raw_attributes_dictionary.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="VA_Hararghe_HDSS - Ethiopia" sheetId="1" r:id="rId1"/>
     <sheet name="VA_IgangaMayuge_HDSS - Uganda" sheetId="2" r:id="rId2"/>
-    <sheet name="VA_MEIRU - Malawi" sheetId="3" r:id="rId3"/>
+    <sheet name="VA_MEIRU_Karonga_HDSS - Malaw" sheetId="3" r:id="rId3"/>
     <sheet name="VA_Niakhar_HDSS - Senegal" sheetId="4" r:id="rId4"/>
     <sheet name="VA_NUHDSS - Kenya" sheetId="5" r:id="rId5"/>
     <sheet name="VA_Ouagadougou_HDSS - Burkina" sheetId="6" r:id="rId6"/>
